--- a/output/第10期計画_社人研推計の町別データの受領点検.xlsx
+++ b/output/第10期計画_社人研推計の町別データの受領点検.xlsx
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>data_ipss_town.py（新規）</t>
+          <t>社人研推計の町別の収録値（新規）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
